--- a/docs/downloads/05/tbl_cooking_marovoay_tous.xlsx
+++ b/docs/downloads/05/tbl_cooking_marovoay_tous.xlsx
@@ -391,7 +391,7 @@
         <v>83</v>
       </c>
       <c r="D2">
-        <v>46.1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -402,14 +402,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C3">
         <v>97</v>
       </c>
       <c r="D3">
-        <v>53.9</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="4">
@@ -427,7 +427,7 @@
         <v>63</v>
       </c>
       <c r="D4">
-        <v>44.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="5">
@@ -438,14 +438,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C5">
         <v>80</v>
       </c>
       <c r="D5">
-        <v>55.9</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -463,7 +463,7 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>14.1</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="7">
@@ -474,14 +474,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C7">
         <v>128</v>
       </c>
       <c r="D7">
-        <v>85.90000000000001</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -499,7 +499,7 @@
         <v>74</v>
       </c>
       <c r="D8">
-        <v>50.7</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="9">
@@ -510,14 +510,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C9">
         <v>72</v>
       </c>
       <c r="D9">
-        <v>49.3</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="10">
@@ -535,7 +535,7 @@
         <v>241</v>
       </c>
       <c r="D10">
-        <v>39</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="11">
@@ -546,14 +546,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C11">
         <v>377</v>
       </c>
       <c r="D11">
-        <v>61</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/05/tbl_cooking_marovoay_tous.xlsx
+++ b/docs/downloads/05/tbl_cooking_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -415,7 +415,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -451,7 +451,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -469,7 +469,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -523,7 +523,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
